--- a/SALTO_GYMNASTICS_2026-03-01_Boys_results.xlsx
+++ b/SALTO_GYMNASTICS_2026-03-01_Boys_results.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mandbt-my.sharepoint.com/personal/cat_mandbt_onmicrosoft_com/Documents/NGL/1ST MARCH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E25D4998-FF2E-4A20-94D1-1B6CB67E6873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{E25D4998-FF2E-4A20-94D1-1B6CB67E6873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8863A1E6-5C09-437A-8D69-A04CD02540FA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Floor" sheetId="1" r:id="rId1"/>
-    <sheet name="Pommel Horse" sheetId="2" r:id="rId2"/>
+    <sheet name="Pommel" sheetId="2" r:id="rId2"/>
     <sheet name="Rings" sheetId="3" r:id="rId3"/>
     <sheet name="Vault" sheetId="4" r:id="rId4"/>
     <sheet name="Parallel Bars" sheetId="5" r:id="rId5"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2325" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="146">
   <si>
     <t>Member ID</t>
   </si>
@@ -843,7 +843,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -855,7 +855,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -884,7 +884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -913,7 +913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -942,7 +942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -971,7 +971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>4133867</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>4829920</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>3372044</v>
       </c>
@@ -2113,7 +2113,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -2125,7 +2125,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>4133867</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>4829920</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>3372044</v>
       </c>
@@ -3383,7 +3383,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -3395,7 +3395,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>4133867</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>4829920</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>3372044</v>
       </c>
@@ -4653,7 +4653,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -4665,7 +4665,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -5477,7 +5477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>4133867</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>4829920</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>3372044</v>
       </c>
@@ -5923,7 +5923,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -5935,7 +5935,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>4133867</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>4829920</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>3372044</v>
       </c>
@@ -7193,7 +7193,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -7205,7 +7205,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -7379,7 +7379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -7437,7 +7437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -7669,7 +7669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -7930,7 +7930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -7959,7 +7959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -8104,7 +8104,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>4133867</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>4829920</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>3372044</v>
       </c>
